--- a/Luban/Excel/情报.xlsx
+++ b/Luban/Excel/情报.xlsx
@@ -1,35 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>think</author>
+  </authors>
+  <commentList>
+    <comment ref="G2" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>think:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 - 自获得开始（x刻）
+2 - 自事件触发（事件id,x刻）
+3 - 固定时间段（开始日期,x刻|结束日期,x刻）</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+  <si>
+    <t>名字</t>
+  </si>
+  <si>
+    <t>效果</t>
+  </si>
+  <si>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>有效期类型</t>
+  </si>
+  <si>
+    <t>有效期</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>#名字</t>
+  </si>
+  <si>
+    <t>#描述</t>
+  </si>
+  <si>
+    <t>#备注</t>
+  </si>
+  <si>
+    <t>int32</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -175,6 +276,17 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -370,12 +482,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -496,138 +623,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -941,12 +1077,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelRow="2"/>
+  <cols>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="19.2222222222222" style="1" customWidth="1"/>
+    <col min="5" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="11.2222222222222" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.2" spans="1:9">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3"/>
+      <c r="G1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" ht="16.2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" ht="16.2" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="2"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -954,7 +1160,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -966,7 +1172,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
